--- a/artfynd/A 23794-2026 artfynd.xlsx
+++ b/artfynd/A 23794-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856917</v>
       </c>
       <c r="B2" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133856916</v>
       </c>
       <c r="B3" t="n">
-        <v>98052</v>
+        <v>98059</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23794-2026 artfynd.xlsx
+++ b/artfynd/A 23794-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133856917</v>
+        <v>133856916</v>
       </c>
       <c r="B2" t="n">
-        <v>99210</v>
+        <v>98066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758005</v>
+        <v>757994</v>
       </c>
       <c r="R2" t="n">
-        <v>7344612</v>
+        <v>7344605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133856916</v>
+        <v>133856917</v>
       </c>
       <c r="B3" t="n">
-        <v>98059</v>
+        <v>99217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757994</v>
+        <v>758005</v>
       </c>
       <c r="R3" t="n">
-        <v>7344605</v>
+        <v>7344612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 23794-2026 artfynd.xlsx
+++ b/artfynd/A 23794-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856916</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133856917</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>